--- a/app/content/changjiang.xlsx
+++ b/app/content/changjiang.xlsx
@@ -928,7 +928,7 @@
         <v>打吃</v>
       </c>
       <c r="C2" t="str">
-        <v>威</v>
+        <v>器</v>
       </c>
       <c r="D2" t="str">
         <v>白子落下，紧气叫吃。</v>
@@ -951,7 +951,7 @@
         <v>守拙</v>
       </c>
       <c r="C3" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D3" t="str">
         <v>稳稳落子，不争一时之地。</v>
@@ -974,7 +974,7 @@
         <v>劫材</v>
       </c>
       <c r="C4" t="str">
-        <v>利</v>
+        <v>策</v>
       </c>
       <c r="D4" t="str">
         <v>打劫，寻一个双方都要应的地方。</v>
@@ -997,7 +997,7 @@
         <v>弃子</v>
       </c>
       <c r="C5" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D5" t="str">
         <v>主动弃掉一块，换全局的活。</v>
@@ -1020,7 +1020,7 @@
         <v>衔枚疾走</v>
       </c>
       <c r="C6" t="str">
-        <v>威</v>
+        <v>器</v>
       </c>
       <c r="D6" t="str">
         <v>马蹄裹布，人不言语，日行八百里。</v>
@@ -1043,7 +1043,7 @@
         <v>断其粮道</v>
       </c>
       <c r="C7" t="str">
-        <v>利</v>
+        <v>策</v>
       </c>
       <c r="D7" t="str">
         <v>烧辎重，绝补给。</v>
@@ -1066,7 +1066,7 @@
         <v>设伏半路</v>
       </c>
       <c r="C8" t="str">
-        <v>理</v>
+        <v>隐</v>
       </c>
       <c r="D8" t="str">
         <v>围魏是虚，打援是实。</v>
@@ -1089,7 +1089,7 @@
         <v>弃辎轻进</v>
       </c>
       <c r="C9" t="str">
-        <v>情</v>
+        <v>器</v>
       </c>
       <c r="D9" t="str">
         <v>缴获全部放弃，俘虏全放，一刻钟拔营。</v>
@@ -1183,7 +1183,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>理,威,情,理,威,情,利</v>
+        <v>策,势,策,策,势,策,策</v>
       </c>
       <c r="I2" t="str">
         <v>c_qi_gong,c_qi_shou,c_qi_jie,c_qi_qi</v>
